--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125337097</v>
+        <v>137260280</v>
       </c>
       <c r="B7" t="n">
-        <v>80298</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,37 +1228,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410028</v>
+        <v>410133</v>
       </c>
       <c r="R7" t="n">
-        <v>6701294</v>
+        <v>6701412</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,12 +1283,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,24 +1313,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125337097</t>
+          <t>https://artportalen.se/Sighting/137260280</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125996620</v>
+        <v>125337097</v>
       </c>
       <c r="B8" t="n">
         <v>80298</v>
@@ -1354,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409861</v>
+        <v>410028</v>
       </c>
       <c r="R8" t="n">
-        <v>6701218</v>
+        <v>6701294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,12 +1395,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,13 +1426,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125996620</t>
+          <t>https://artportalen.se/Sighting/125337097</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129296543</v>
+        <v>125996620</v>
       </c>
       <c r="B9" t="n">
         <v>80298</v>
@@ -1452,17 +1463,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410021</v>
+        <v>409861</v>
       </c>
       <c r="R9" t="n">
-        <v>6701299</v>
+        <v>6701218</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,17 +1497,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,34 +1511,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296543</t>
+          <t>https://artportalen.se/Sighting/125996620</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124191609</v>
+        <v>129296543</v>
       </c>
       <c r="B10" t="n">
-        <v>81312</v>
+        <v>80298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,37 +1545,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>388</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410171</v>
+        <v>410021</v>
       </c>
       <c r="R10" t="n">
-        <v>6701395</v>
+        <v>6701299</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1594,12 +1599,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,30 +1618,31 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124191609</t>
+          <t>https://artportalen.se/Sighting/129296543</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124230024</v>
+        <v>124191609</v>
       </c>
       <c r="B11" t="n">
         <v>81312</v>
@@ -1666,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410109</v>
+        <v>410171</v>
       </c>
       <c r="R11" t="n">
-        <v>6701358</v>
+        <v>6701395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,16 +1738,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124230024</t>
+          <t>https://artportalen.se/Sighting/124191609</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125337855</v>
+        <v>124230024</v>
       </c>
       <c r="B12" t="n">
-        <v>80433</v>
+        <v>81312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,21 +1755,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410092</v>
+        <v>410109</v>
       </c>
       <c r="R12" t="n">
-        <v>6701521</v>
+        <v>6701358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,12 +1809,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,49 +1829,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125337855</t>
+          <t>https://artportalen.se/Sighting/124230024</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125337220</v>
+        <v>125337855</v>
       </c>
       <c r="B13" t="n">
-        <v>91966</v>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5321</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1870,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410028</v>
+        <v>410092</v>
       </c>
       <c r="R13" t="n">
-        <v>6701296</v>
+        <v>6701521</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,38 +1942,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125337220</t>
+          <t>https://artportalen.se/Sighting/125337855</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125996990</v>
+        <v>125337220</v>
       </c>
       <c r="B14" t="n">
-        <v>91738</v>
+        <v>91966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6020</v>
+        <v>5321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409870</v>
+        <v>410028</v>
       </c>
       <c r="R14" t="n">
-        <v>6701239</v>
+        <v>6701296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,12 +2013,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2033,51 +2044,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125996990</t>
+          <t>https://artportalen.se/Sighting/125337220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97748895</v>
+        <v>125996990</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>91738</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6020</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410187</v>
+        <v>409870</v>
       </c>
       <c r="R15" t="n">
-        <v>6701551</v>
+        <v>6701239</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,12 +2115,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2124,24 +2135,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97748895</t>
+          <t>https://artportalen.se/Sighting/125996990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123266817</v>
+        <v>97748895</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2170,22 +2181,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409797</v>
+        <v>410187</v>
       </c>
       <c r="R16" t="n">
-        <v>6701306</v>
+        <v>6701551</v>
       </c>
       <c r="S16" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2209,22 +2217,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,24 +2237,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123266817</t>
+          <t>https://artportalen.se/Sighting/97748895</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123266941</v>
+        <v>123266817</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2294,13 +2292,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409810</v>
+        <v>409797</v>
       </c>
       <c r="R17" t="n">
-        <v>6701318</v>
+        <v>6701306</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,7 +2327,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2339,7 +2337,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2354,24 +2352,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123266941</t>
+          <t>https://artportalen.se/Sighting/123266817</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123270753</v>
+        <v>123266941</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2405,17 +2403,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409927</v>
+        <v>409810</v>
       </c>
       <c r="R18" t="n">
-        <v>6701337</v>
+        <v>6701318</v>
       </c>
       <c r="S18" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2444,7 +2442,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2454,7 +2452,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,13 +2478,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123270753</t>
+          <t>https://artportalen.se/Sighting/123266941</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124190554</v>
+        <v>123270753</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2515,19 +2513,22 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410171</v>
+        <v>409927</v>
       </c>
       <c r="R19" t="n">
-        <v>6701395</v>
+        <v>6701337</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2551,12 +2552,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,24 +2582,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124190554</t>
+          <t>https://artportalen.se/Sighting/123270753</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124229574</v>
+        <v>124190554</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2623,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410109</v>
+        <v>410171</v>
       </c>
       <c r="R20" t="n">
-        <v>6701358</v>
+        <v>6701395</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,12 +2664,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2684,38 +2695,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124229574</t>
+          <t>https://artportalen.se/Sighting/124190554</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124191699</v>
+        <v>124229574</v>
       </c>
       <c r="B21" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410171</v>
+        <v>410109</v>
       </c>
       <c r="R21" t="n">
-        <v>6701395</v>
+        <v>6701358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,12 +2766,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2786,13 +2797,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124191699</t>
+          <t>https://artportalen.se/Sighting/124229574</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124193734</v>
+        <v>124191699</v>
       </c>
       <c r="B22" t="n">
         <v>79946</v>
@@ -2827,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409987</v>
+        <v>410171</v>
       </c>
       <c r="R22" t="n">
-        <v>6701363</v>
+        <v>6701395</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2888,13 +2899,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124193734</t>
+          <t>https://artportalen.se/Sighting/124191699</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124194211</v>
+        <v>124193734</v>
       </c>
       <c r="B23" t="n">
         <v>79946</v>
@@ -2929,10 +2940,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409871</v>
+        <v>409987</v>
       </c>
       <c r="R23" t="n">
-        <v>6701373</v>
+        <v>6701363</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,16 +3001,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124194211</t>
+          <t>https://artportalen.se/Sighting/124193734</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97748887</v>
+        <v>124194211</v>
       </c>
       <c r="B24" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3007,34 +3018,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409878</v>
+        <v>409871</v>
       </c>
       <c r="R24" t="n">
-        <v>6701306</v>
+        <v>6701373</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,12 +3072,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3081,24 +3092,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97748887</t>
+          <t>https://artportalen.se/Sighting/124194211</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97748891</v>
+        <v>97748887</v>
       </c>
       <c r="B25" t="n">
         <v>80432</v>
@@ -3133,10 +3144,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410055</v>
+        <v>409878</v>
       </c>
       <c r="R25" t="n">
-        <v>6701497</v>
+        <v>6701306</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3171,11 +3182,6 @@
           <t>2021-09-14</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På stående gammal asp.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3199,13 +3205,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97748891</t>
+          <t>https://artportalen.se/Sighting/97748887</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124192913</v>
+        <v>97748891</v>
       </c>
       <c r="B26" t="n">
         <v>80432</v>
@@ -3236,14 +3242,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410095</v>
+        <v>410055</v>
       </c>
       <c r="R26" t="n">
-        <v>6701528</v>
+        <v>6701497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,12 +3276,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På stående gammal asp.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3290,24 +3301,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124192913</t>
+          <t>https://artportalen.se/Sighting/97748891</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124231394</v>
+        <v>124192913</v>
       </c>
       <c r="B27" t="n">
         <v>80432</v>
@@ -3342,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410055</v>
+        <v>410095</v>
       </c>
       <c r="R27" t="n">
-        <v>6701334</v>
+        <v>6701528</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,12 +3383,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3403,13 +3414,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124231394</t>
+          <t>https://artportalen.se/Sighting/124192913</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125337105</v>
+        <v>124231394</v>
       </c>
       <c r="B28" t="n">
         <v>80432</v>
@@ -3444,10 +3455,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410028</v>
+        <v>410055</v>
       </c>
       <c r="R28" t="n">
-        <v>6701294</v>
+        <v>6701334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,12 +3485,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3494,24 +3505,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125337105</t>
+          <t>https://artportalen.se/Sighting/124231394</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125996629</v>
+        <v>125337105</v>
       </c>
       <c r="B29" t="n">
         <v>80432</v>
@@ -3546,10 +3557,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409865</v>
+        <v>410028</v>
       </c>
       <c r="R29" t="n">
-        <v>6701219</v>
+        <v>6701294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3576,12 +3587,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3607,13 +3618,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125996629</t>
+          <t>https://artportalen.se/Sighting/125337105</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125997099</v>
+        <v>125996629</v>
       </c>
       <c r="B30" t="n">
         <v>80432</v>
@@ -3648,10 +3659,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409876</v>
+        <v>409865</v>
       </c>
       <c r="R30" t="n">
-        <v>6701314</v>
+        <v>6701219</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3709,38 +3720,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125997099</t>
+          <t>https://artportalen.se/Sighting/125996629</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124231452</v>
+        <v>125997099</v>
       </c>
       <c r="B31" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3750,10 +3761,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410055</v>
+        <v>409876</v>
       </c>
       <c r="R31" t="n">
-        <v>6701334</v>
+        <v>6701314</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3780,12 +3791,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3800,65 +3811,65 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124231452</t>
+          <t>https://artportalen.se/Sighting/125997099</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125337110</v>
+        <v>137260791</v>
       </c>
       <c r="B32" t="n">
-        <v>80467</v>
+        <v>80618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410028</v>
+        <v>410273</v>
       </c>
       <c r="R32" t="n">
-        <v>6701296</v>
+        <v>6701589</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3882,12 +3893,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3902,27 +3923,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125337110</t>
+          <t>https://artportalen.se/Sighting/137260791</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129296565</v>
+        <v>124231452</v>
       </c>
       <c r="B33" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3930,37 +3951,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410013</v>
+        <v>410055</v>
       </c>
       <c r="R33" t="n">
-        <v>6701302</v>
+        <v>6701334</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3984,12 +4005,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4004,67 +4025,62 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129296565</t>
+          <t>https://artportalen.se/Sighting/124231452</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125339785</v>
+        <v>125337110</v>
       </c>
       <c r="B34" t="n">
-        <v>57953</v>
+        <v>80467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>410362</v>
+        <v>410028</v>
       </c>
       <c r="R34" t="n">
-        <v>6701601</v>
+        <v>6701296</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4099,11 +4115,6 @@
           <t>2025-05-23</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4127,54 +4138,54 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125339785</t>
+          <t>https://artportalen.se/Sighting/125337110</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125996810</v>
+        <v>129296565</v>
       </c>
       <c r="B35" t="n">
-        <v>99118</v>
+        <v>80467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409870</v>
+        <v>410013</v>
       </c>
       <c r="R35" t="n">
-        <v>6701239</v>
+        <v>6701302</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4198,12 +4209,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4218,62 +4229,67 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125996810</t>
+          <t>https://artportalen.se/Sighting/129296565</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>97748886</v>
+        <v>125339785</v>
       </c>
       <c r="B36" t="n">
-        <v>80392</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409912</v>
+        <v>410362</v>
       </c>
       <c r="R36" t="n">
-        <v>6701292</v>
+        <v>6701601</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4300,12 +4316,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4320,62 +4341,62 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97748886</t>
+          <t>https://artportalen.se/Sighting/125339785</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>97748896</v>
+        <v>125996810</v>
       </c>
       <c r="B37" t="n">
-        <v>80392</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410056</v>
+        <v>409870</v>
       </c>
       <c r="R37" t="n">
-        <v>6701502</v>
+        <v>6701239</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4402,12 +4423,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4422,24 +4443,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97748896</t>
+          <t>https://artportalen.se/Sighting/125996810</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124231730</v>
+        <v>97748886</v>
       </c>
       <c r="B38" t="n">
         <v>80392</v>
@@ -4470,14 +4491,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410055</v>
+        <v>409912</v>
       </c>
       <c r="R38" t="n">
-        <v>6701334</v>
+        <v>6701292</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4504,12 +4525,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4524,24 +4545,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124231730</t>
+          <t>https://artportalen.se/Sighting/97748886</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124232245</v>
+        <v>97748896</v>
       </c>
       <c r="B39" t="n">
         <v>80392</v>
@@ -4572,14 +4593,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409907</v>
+        <v>410056</v>
       </c>
       <c r="R39" t="n">
-        <v>6701308</v>
+        <v>6701502</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,12 +4627,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4626,24 +4647,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124232245</t>
+          <t>https://artportalen.se/Sighting/97748896</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125337108</v>
+        <v>124231730</v>
       </c>
       <c r="B40" t="n">
         <v>80392</v>
@@ -4678,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410028</v>
+        <v>410055</v>
       </c>
       <c r="R40" t="n">
-        <v>6701296</v>
+        <v>6701334</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,12 +4729,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4728,24 +4749,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125337108</t>
+          <t>https://artportalen.se/Sighting/124231730</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125996642</v>
+        <v>124232245</v>
       </c>
       <c r="B41" t="n">
         <v>80392</v>
@@ -4780,10 +4801,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409862</v>
+        <v>409907</v>
       </c>
       <c r="R41" t="n">
-        <v>6701218</v>
+        <v>6701308</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,12 +4831,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4830,24 +4851,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125996642</t>
+          <t>https://artportalen.se/Sighting/124232245</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125997105</v>
+        <v>125337108</v>
       </c>
       <c r="B42" t="n">
         <v>80392</v>
@@ -4882,10 +4903,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409874</v>
+        <v>410028</v>
       </c>
       <c r="R42" t="n">
-        <v>6701309</v>
+        <v>6701296</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,12 +4933,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,16 +4964,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125997105</t>
+          <t>https://artportalen.se/Sighting/125337108</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125996612</v>
+        <v>125996642</v>
       </c>
       <c r="B43" t="n">
-        <v>80357</v>
+        <v>80392</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4960,21 +4981,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003719</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4984,10 +5005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409865</v>
+        <v>409862</v>
       </c>
       <c r="R43" t="n">
-        <v>6701222</v>
+        <v>6701218</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5044,6 +5065,210 @@
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125996642</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125997105</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>409874</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6701309</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125997105</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125996612</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80357</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>409865</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6701222</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125996612</t>
         </is>
@@ -5093,6 +5318,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>137260280</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>137260791</v>
       </c>
       <c r="B32" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>137260280</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>137260791</v>
       </c>
       <c r="B32" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>137260280</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>137260791</v>
       </c>
       <c r="B32" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>137260280</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>137260791</v>
       </c>
       <c r="B32" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>137260280</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>137260791</v>
       </c>
       <c r="B32" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>137260280</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>137260791</v>
       </c>
       <c r="B32" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>137260280</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>137260791</v>
       </c>
       <c r="B32" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
